--- a/analise convertidos.xlsx
+++ b/analise convertidos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mirly Queiroz\Desktop\ANS VTos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{67358EF4-7F34-41A0-B168-01A7C5438225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{749E5448-7378-4996-AF6A-24C6B6D0B8D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{1C476FF1-CB4B-4197-9ED1-7B6217F7E60E}"/>
   </bookViews>
@@ -499,7 +499,7 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -510,7 +510,7 @@
         <v>6</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -521,7 +521,7 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>50</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -532,7 +532,7 @@
         <v>8</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -543,7 +543,7 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>33</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -554,7 +554,7 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -565,7 +565,7 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>21</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -576,7 +576,7 @@
         <v>14</v>
       </c>
       <c r="C9">
-        <v>28</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -587,7 +587,7 @@
         <v>15</v>
       </c>
       <c r="C10">
-        <v>15</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -598,7 +598,7 @@
         <v>16</v>
       </c>
       <c r="C11">
-        <v>25</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -609,7 +609,7 @@
         <v>17</v>
       </c>
       <c r="C12">
-        <v>25</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -620,7 +620,7 @@
         <v>18</v>
       </c>
       <c r="C13">
-        <v>32</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -631,7 +631,7 @@
         <v>19</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -642,7 +642,7 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>20</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -653,7 +653,7 @@
         <v>16</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -664,7 +664,7 @@
         <v>16</v>
       </c>
       <c r="C17">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -675,7 +675,7 @@
         <v>23</v>
       </c>
       <c r="C18">
-        <v>31</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -686,7 +686,7 @@
         <v>14</v>
       </c>
       <c r="C19">
-        <v>22</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -697,7 +697,7 @@
         <v>16</v>
       </c>
       <c r="C20">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -708,7 +708,7 @@
         <v>18</v>
       </c>
       <c r="C21">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -719,7 +719,7 @@
         <v>19</v>
       </c>
       <c r="C22">
-        <v>16</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -730,7 +730,7 @@
         <v>25</v>
       </c>
       <c r="C23">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -741,7 +741,7 @@
         <v>14</v>
       </c>
       <c r="C24">
-        <v>37</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -752,7 +752,7 @@
         <v>26</v>
       </c>
       <c r="C25">
-        <v>19</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -763,7 +763,7 @@
         <v>28</v>
       </c>
       <c r="C26">
-        <v>15</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
